--- a/dados/BA.xlsx
+++ b/dados/BA.xlsx
@@ -82,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
@@ -115,6 +115,9 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -192,7 +195,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_BA" displayName="Tabela_BA" ref="A1:X449" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_BA" displayName="Tabela_BA" ref="A1:X465" headerRowCount="1">
   <autoFilter ref="A1:X449"/>
   <tableColumns count="24">
     <tableColumn id="1" name="ID"/>
@@ -489,7 +492,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X449"/>
+  <dimension ref="A1:X465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" customWidth="1" min="1" max="1"/>
@@ -47013,6 +47016,1595 @@
         </is>
       </c>
     </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>BA9</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>RGB(128,0,128)</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>BA-EUNAPOLIS_ITABELA</t>
+        </is>
+      </c>
+      <c r="D450" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E450" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F450" s="13" t="n">
+        <v>603.0992</v>
+      </c>
+      <c r="G450" s="13" t="n">
+        <v>11449.49</v>
+      </c>
+      <c r="H450" s="13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>RDQ4C93</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, JOAO MARQUES CARDOSO</t>
+        </is>
+      </c>
+      <c r="K450" s="14" t="n">
+        <v>349.46</v>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N450" t="inlineStr">
+        <is>
+          <t>20/08/2026 19:05 BRT</t>
+        </is>
+      </c>
+      <c r="O450" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P450" t="inlineStr">
+        <is>
+          <t>20/08/2026 18:59 BRT</t>
+        </is>
+      </c>
+      <c r="Q450" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S450" t="inlineStr">
+        <is>
+          <t>TOCO-II</t>
+        </is>
+      </c>
+      <c r="T450" t="inlineStr">
+        <is>
+          <t>21/08/2026 - SEXTA-FEIRA</t>
+        </is>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V450" s="9">
+        <f>IFERROR(F450/H450,"")</f>
+        <v/>
+      </c>
+      <c r="W450" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X450" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>BA12</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>RGB(218,165,32)</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>BA-PORTO_BAIANAO</t>
+        </is>
+      </c>
+      <c r="D451" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="E451" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F451" s="13" t="n">
+        <v>940.2430000000001</v>
+      </c>
+      <c r="G451" s="13" t="n">
+        <v>14018.31</v>
+      </c>
+      <c r="H451" s="13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>TPV1D53</t>
+        </is>
+      </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ARICLENES SANTOS GARCIA</t>
+        </is>
+      </c>
+      <c r="K451" s="14" t="n">
+        <v>410.09</v>
+      </c>
+      <c r="M451" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N451" t="inlineStr">
+        <is>
+          <t>20/08/2026 19:05 BRT</t>
+        </is>
+      </c>
+      <c r="O451" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P451" t="inlineStr">
+        <is>
+          <t>20/08/2026 18:59 BRT</t>
+        </is>
+      </c>
+      <c r="Q451" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S451" t="inlineStr">
+        <is>
+          <t>TOCO-II</t>
+        </is>
+      </c>
+      <c r="T451" t="inlineStr">
+        <is>
+          <t>21/08/2026 - SEXTA-FEIRA</t>
+        </is>
+      </c>
+      <c r="U451" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V451" s="9">
+        <f>IFERROR(F451/H451,"")</f>
+        <v/>
+      </c>
+      <c r="W451" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X451" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>BA5</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>RGB(255,105,180)</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>BA-ITAMARAJU_PRADO</t>
+        </is>
+      </c>
+      <c r="D452" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="E452" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="F452" s="13" t="n">
+        <v>1231.6025</v>
+      </c>
+      <c r="G452" s="13" t="n">
+        <v>19678.18</v>
+      </c>
+      <c r="H452" s="13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>RDN3H40</t>
+        </is>
+      </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ALEX SANDRO RIBEIRO NOVAIS</t>
+        </is>
+      </c>
+      <c r="K452" s="14" t="n">
+        <v>223.72</v>
+      </c>
+      <c r="M452" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N452" t="inlineStr">
+        <is>
+          <t>20/08/2026 19:05 BRT</t>
+        </is>
+      </c>
+      <c r="O452" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P452" t="inlineStr">
+        <is>
+          <t>20/08/2026 18:59 BRT</t>
+        </is>
+      </c>
+      <c r="Q452" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S452" t="inlineStr">
+        <is>
+          <t>TOCO-II</t>
+        </is>
+      </c>
+      <c r="T452" t="inlineStr">
+        <is>
+          <t>21/08/2026 - SEXTA-FEIRA</t>
+        </is>
+      </c>
+      <c r="U452" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V452" s="9">
+        <f>IFERROR(F452/H452,"")</f>
+        <v/>
+      </c>
+      <c r="W452" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X452" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>BA4</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>RGB(0,0,255)</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>BA-ALCOBACA-CARAVELAS</t>
+        </is>
+      </c>
+      <c r="D453" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="E453" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="F453" s="13" t="n">
+        <v>1603.051</v>
+      </c>
+      <c r="G453" s="13" t="n">
+        <v>23932.7</v>
+      </c>
+      <c r="H453" s="13" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>PLA2587</t>
+        </is>
+      </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, BENEDITO FELIX ANTONIO</t>
+        </is>
+      </c>
+      <c r="K453" s="14" t="n">
+        <v>237.78</v>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>20/08/2026 19:05 BRT</t>
+        </is>
+      </c>
+      <c r="O453" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P453" t="inlineStr">
+        <is>
+          <t>20/08/2026 18:59 BRT</t>
+        </is>
+      </c>
+      <c r="Q453" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S453" t="inlineStr">
+        <is>
+          <t>TOCO</t>
+        </is>
+      </c>
+      <c r="T453" t="inlineStr">
+        <is>
+          <t>21/08/2026 - SEXTA-FEIRA</t>
+        </is>
+      </c>
+      <c r="U453" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V453" s="9">
+        <f>IFERROR(F453/H453,"")</f>
+        <v/>
+      </c>
+      <c r="W453" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X453" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>BA1</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>RGB(220,20,60)</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>BA-TEIXEIRA_FREITAS</t>
+        </is>
+      </c>
+      <c r="D454" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="E454" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="F454" s="13" t="n">
+        <v>1865.2838</v>
+      </c>
+      <c r="G454" s="13" t="n">
+        <v>27439.6</v>
+      </c>
+      <c r="H454" s="13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>QRE9E97</t>
+        </is>
+      </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, COSME FERREIRA GOMES</t>
+        </is>
+      </c>
+      <c r="K454" s="14" t="n">
+        <v>33.64</v>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>20/08/2026 19:05 BRT</t>
+        </is>
+      </c>
+      <c r="O454" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P454" t="inlineStr">
+        <is>
+          <t>20/08/2026 18:59 BRT</t>
+        </is>
+      </c>
+      <c r="Q454" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S454" t="inlineStr">
+        <is>
+          <t>TOCO-II</t>
+        </is>
+      </c>
+      <c r="T454" t="inlineStr">
+        <is>
+          <t>21/08/2026 - SEXTA-FEIRA</t>
+        </is>
+      </c>
+      <c r="U454" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V454" s="9">
+        <f>IFERROR(F454/H454,"")</f>
+        <v/>
+      </c>
+      <c r="W454" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X454" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>BA15</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>RGB(210,105,30)</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>BA-PORTO_CABRALIA</t>
+        </is>
+      </c>
+      <c r="D455" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="E455" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="F455" s="13" t="n">
+        <v>1441.818</v>
+      </c>
+      <c r="G455" s="13" t="n">
+        <v>21291.95</v>
+      </c>
+      <c r="H455" s="13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>TQG6B12</t>
+        </is>
+      </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, DIRCEU KATO KATAYAMA</t>
+        </is>
+      </c>
+      <c r="K455" s="14" t="n">
+        <v>468.06</v>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>21/08/2026 00:39 BRT</t>
+        </is>
+      </c>
+      <c r="O455" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P455" t="inlineStr">
+        <is>
+          <t>20/08/2026 18:59 BRT</t>
+        </is>
+      </c>
+      <c r="Q455" t="inlineStr">
+        <is>
+          <t>exceptiongeneratorprocess</t>
+        </is>
+      </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>DIRCEU KATO KATAYAMA</t>
+        </is>
+      </c>
+      <c r="S455" t="inlineStr">
+        <is>
+          <t>TOCO-II</t>
+        </is>
+      </c>
+      <c r="T455" t="inlineStr">
+        <is>
+          <t>21/08/2026 - SEXTA-FEIRA</t>
+        </is>
+      </c>
+      <c r="U455" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="V455" s="9">
+        <f>IFERROR(F455/H455,"")</f>
+        <v/>
+      </c>
+      <c r="W455" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X455" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D456" s="12" t="n">
+        <v>134</v>
+      </c>
+      <c r="E456" s="12" t="n">
+        <v>147</v>
+      </c>
+      <c r="F456" s="13" t="n">
+        <v>7685.0975</v>
+      </c>
+      <c r="G456" s="13" t="n">
+        <v>117810.23</v>
+      </c>
+      <c r="H456" s="13" t="n">
+        <v>38000</v>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K456" s="14" t="n">
+        <v>1722.75</v>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O456" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="P456" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Q456" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="R456" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="S456" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="T456" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="U456" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V456" s="9">
+        <f>IFERROR(F456/H456,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>SF3</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>BA-BELMONTE</t>
+        </is>
+      </c>
+      <c r="D457" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="E457" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="F457" s="13" t="n">
+        <v>1237.807</v>
+      </c>
+      <c r="G457" s="13" t="n">
+        <v>21473.5</v>
+      </c>
+      <c r="H457" s="13" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>PKU5I64</t>
+        </is>
+      </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, JOSE AILTON SERQUEIRA DE JESUS</t>
+        </is>
+      </c>
+      <c r="K457" s="14" t="n">
+        <v>284.62</v>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>20/08/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="O457" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P457" t="inlineStr">
+        <is>
+          <t>20/08/2026 16:51 BRT</t>
+        </is>
+      </c>
+      <c r="Q457" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S457" t="inlineStr">
+        <is>
+          <t>TOCO-III</t>
+        </is>
+      </c>
+      <c r="T457" t="inlineStr">
+        <is>
+          <t>21/08/2026 - SUL-FRIOS SEXTA</t>
+        </is>
+      </c>
+      <c r="U457" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V457" s="9">
+        <f>IFERROR(F457/H457,"")</f>
+        <v/>
+      </c>
+      <c r="W457" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X457" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>BPS1</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>RGB(220,20,60)</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>BA-PORTO_CENTRO-ORLA</t>
+        </is>
+      </c>
+      <c r="D458" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E458" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="F458" s="13" t="n">
+        <v>1086.1422</v>
+      </c>
+      <c r="G458" s="13" t="n">
+        <v>20303.56</v>
+      </c>
+      <c r="H458" s="13" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>ISP5356</t>
+        </is>
+      </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, DEIVID DE SOUZA</t>
+        </is>
+      </c>
+      <c r="K458" s="14" t="n">
+        <v>50.89</v>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>20/08/2026 16:40 BRT</t>
+        </is>
+      </c>
+      <c r="O458" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P458" t="inlineStr">
+        <is>
+          <t>20/08/2026 16:11 BRT</t>
+        </is>
+      </c>
+      <c r="Q458" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S458" t="inlineStr">
+        <is>
+          <t>VUC</t>
+        </is>
+      </c>
+      <c r="T458" t="inlineStr">
+        <is>
+          <t>21/08/2026 - PORTO-IMPORT SEXTA</t>
+        </is>
+      </c>
+      <c r="U458" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V458" s="9">
+        <f>IFERROR(F458/H458,"")</f>
+        <v/>
+      </c>
+      <c r="W458" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X458" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>SF1</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>RGB(220,20,60)</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>BA-EUNAPOLIS</t>
+        </is>
+      </c>
+      <c r="D459" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="E459" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="F459" s="13" t="n">
+        <v>1727.6112</v>
+      </c>
+      <c r="G459" s="13" t="n">
+        <v>23231.82</v>
+      </c>
+      <c r="H459" s="13" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>TPP2D15</t>
+        </is>
+      </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, RAYNELLE RUBIO SIQUEIRA D ALESSANDRO</t>
+        </is>
+      </c>
+      <c r="K459" s="14" t="n">
+        <v>87.20999999999999</v>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>20/08/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="O459" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P459" t="inlineStr">
+        <is>
+          <t>20/08/2026 16:51 BRT</t>
+        </is>
+      </c>
+      <c r="Q459" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S459" t="inlineStr">
+        <is>
+          <t>TOCO-III</t>
+        </is>
+      </c>
+      <c r="T459" t="inlineStr">
+        <is>
+          <t>21/08/2026 - SUL-FRIOS SEXTA</t>
+        </is>
+      </c>
+      <c r="U459" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V459" s="9">
+        <f>IFERROR(F459/H459,"")</f>
+        <v/>
+      </c>
+      <c r="W459" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X459" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>BPS2</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>BA-ARAIAL_DAJUDA</t>
+        </is>
+      </c>
+      <c r="D460" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="E460" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="F460" s="13" t="n">
+        <v>1302.188</v>
+      </c>
+      <c r="G460" s="13" t="n">
+        <v>27021.95</v>
+      </c>
+      <c r="H460" s="13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>TQG6D22</t>
+        </is>
+      </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, FABIANO JESUS DA HORA</t>
+        </is>
+      </c>
+      <c r="K460" s="14" t="n">
+        <v>38.17</v>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>20/08/2026 16:40 BRT</t>
+        </is>
+      </c>
+      <c r="O460" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P460" t="inlineStr">
+        <is>
+          <t>20/08/2026 16:11 BRT</t>
+        </is>
+      </c>
+      <c r="Q460" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S460" t="inlineStr">
+        <is>
+          <t>TOCO-II</t>
+        </is>
+      </c>
+      <c r="T460" t="inlineStr">
+        <is>
+          <t>21/08/2026 - PORTO-IMPORT SEXTA</t>
+        </is>
+      </c>
+      <c r="U460" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V460" s="9">
+        <f>IFERROR(F460/H460,"")</f>
+        <v/>
+      </c>
+      <c r="W460" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X460" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>BPS4</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>RGB(0,0,255)</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>BA-TRANCOSO</t>
+        </is>
+      </c>
+      <c r="D461" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="E461" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="F461" s="13" t="n">
+        <v>1698.3058</v>
+      </c>
+      <c r="G461" s="13" t="n">
+        <v>35542.2</v>
+      </c>
+      <c r="H461" s="13" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>PJN2J39</t>
+        </is>
+      </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, AMARILTON JESUS SANTOS</t>
+        </is>
+      </c>
+      <c r="K461" s="14" t="n">
+        <v>125.35</v>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>20/08/2026 16:40 BRT</t>
+        </is>
+      </c>
+      <c r="O461" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P461" t="inlineStr">
+        <is>
+          <t>20/08/2026 16:11 BRT</t>
+        </is>
+      </c>
+      <c r="Q461" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S461" t="inlineStr">
+        <is>
+          <t>TOCO</t>
+        </is>
+      </c>
+      <c r="T461" t="inlineStr">
+        <is>
+          <t>21/08/2026 - PORTO-IMPORT SEXTA</t>
+        </is>
+      </c>
+      <c r="U461" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V461" s="9">
+        <f>IFERROR(F461/H461,"")</f>
+        <v/>
+      </c>
+      <c r="W461" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X461" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>SF5</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>RGB(0,0,255)</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>BA-PRADO</t>
+        </is>
+      </c>
+      <c r="D462" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="E462" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F462" s="13" t="n">
+        <v>2912.4155</v>
+      </c>
+      <c r="G462" s="13" t="n">
+        <v>38488.42</v>
+      </c>
+      <c r="H462" s="13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>TQG6C72</t>
+        </is>
+      </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, RUY CHARELS CARVALHO DE JESUS</t>
+        </is>
+      </c>
+      <c r="K462" s="14" t="n">
+        <v>418.52</v>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>20/08/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="O462" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P462" t="inlineStr">
+        <is>
+          <t>20/08/2026 16:51 BRT</t>
+        </is>
+      </c>
+      <c r="Q462" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S462" t="inlineStr">
+        <is>
+          <t>TOCO-II</t>
+        </is>
+      </c>
+      <c r="T462" t="inlineStr">
+        <is>
+          <t>21/08/2026 - SUL-FRIOS SEXTA</t>
+        </is>
+      </c>
+      <c r="U462" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V462" s="9">
+        <f>IFERROR(F462/H462,"")</f>
+        <v/>
+      </c>
+      <c r="W462" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X462" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>SF4</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>RGB(255,140,0)</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>BA-CABRALIA/ORLA</t>
+        </is>
+      </c>
+      <c r="D463" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="E463" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="F463" s="13" t="n">
+        <v>4277.2355</v>
+      </c>
+      <c r="G463" s="13" t="n">
+        <v>60228.5</v>
+      </c>
+      <c r="H463" s="13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>TQG7B12</t>
+        </is>
+      </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, THIAGO MACHADO DE SOUZA</t>
+        </is>
+      </c>
+      <c r="K463" s="14" t="n">
+        <v>228.88</v>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>20/08/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="O463" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P463" t="inlineStr">
+        <is>
+          <t>20/08/2026 16:51 BRT</t>
+        </is>
+      </c>
+      <c r="Q463" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S463" t="inlineStr">
+        <is>
+          <t>TOCO-II</t>
+        </is>
+      </c>
+      <c r="T463" t="inlineStr">
+        <is>
+          <t>21/08/2026 - SUL-FRIOS SEXTA</t>
+        </is>
+      </c>
+      <c r="U463" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V463" s="9">
+        <f>IFERROR(F463/H463,"")</f>
+        <v/>
+      </c>
+      <c r="W463" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X463" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>SF2</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>RGB(139,0,0)</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>PORTO_SEGURO-BAIRROS</t>
+        </is>
+      </c>
+      <c r="D464" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="E464" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F464" s="13" t="n">
+        <v>3596.2425</v>
+      </c>
+      <c r="G464" s="13" t="n">
+        <v>53721.55</v>
+      </c>
+      <c r="H464" s="13" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>TPP2C65</t>
+        </is>
+      </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, JILVAN DE JESUS OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="K464" s="14" t="n">
+        <v>160.24</v>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>20/08/2026 18:32 BRT</t>
+        </is>
+      </c>
+      <c r="O464" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P464" t="inlineStr">
+        <is>
+          <t>20/08/2026 16:51 BRT</t>
+        </is>
+      </c>
+      <c r="Q464" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S464" t="inlineStr">
+        <is>
+          <t>TOCO-III</t>
+        </is>
+      </c>
+      <c r="T464" t="inlineStr">
+        <is>
+          <t>21/08/2026 - SUL-FRIOS SEXTA</t>
+        </is>
+      </c>
+      <c r="U464" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V464" s="9">
+        <f>IFERROR(F464/H464,"")</f>
+        <v/>
+      </c>
+      <c r="W464" t="inlineStr">
+        <is>
+          <t>21/08</t>
+        </is>
+      </c>
+      <c r="X464" t="inlineStr">
+        <is>
+          <t>AGO/S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D465" s="12" t="n">
+        <v>216</v>
+      </c>
+      <c r="E465" s="12" t="n">
+        <v>234</v>
+      </c>
+      <c r="F465" s="13" t="n">
+        <v>17837.9477</v>
+      </c>
+      <c r="G465" s="13" t="n">
+        <v>280011.5</v>
+      </c>
+      <c r="H465" s="13" t="n">
+        <v>49700</v>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="K465" s="14" t="n">
+        <v>1393.88</v>
+      </c>
+      <c r="L465" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="O465" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="P465" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="Q465" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="S465" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="T465" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="U465" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="V465" s="9">
+        <f>IFERROR(F465/H465,"")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>

--- a/dados/BA.xlsx
+++ b/dados/BA.xlsx
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_BA" displayName="Tabela_BA" ref="A1:X500" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela_BA" displayName="Tabela_BA" ref="A1:X515" headerRowCount="1">
   <autoFilter ref="A1:X483"/>
   <tableColumns count="24">
     <tableColumn id="1" name="ID"/>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X500"/>
+  <dimension ref="A1:X515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10.5703125" customWidth="1" min="1" max="1"/>
@@ -52277,6 +52277,1501 @@
         <v/>
       </c>
     </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>BA15</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>RGB(210,105,30)</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>BA-EUNAPOLIS/ITABELA</t>
+        </is>
+      </c>
+      <c r="D501" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E501" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="F501" s="13" t="n">
+        <v>322.7514</v>
+      </c>
+      <c r="G501" s="13" t="n">
+        <v>4890.74</v>
+      </c>
+      <c r="H501" s="13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>TPV1D53</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, JOAO MARQUES CARDOSO</t>
+        </is>
+      </c>
+      <c r="K501" s="14" t="n">
+        <v>352.18</v>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>25/08/2026 19:06 BRT</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:38 BRT</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S501" t="inlineStr">
+        <is>
+          <t>TOCO-II</t>
+        </is>
+      </c>
+      <c r="T501" t="inlineStr">
+        <is>
+          <t>26/08/2026 - QUARTA-FEIRA</t>
+        </is>
+      </c>
+      <c r="U501" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V501" s="9">
+        <f>IFERROR(F501/H501,"")</f>
+        <v/>
+      </c>
+      <c r="W501" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X501" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>BA8</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>RGB(70,130,180)</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>BA-ALCOBACA-PRADO</t>
+        </is>
+      </c>
+      <c r="D502" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="E502" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="F502" s="13" t="n">
+        <v>1512.5224</v>
+      </c>
+      <c r="G502" s="13" t="n">
+        <v>25202.13</v>
+      </c>
+      <c r="H502" s="13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>RDQ4C93</t>
+        </is>
+      </c>
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ALEX SANDRO RIBEIRO NOVAIS</t>
+        </is>
+      </c>
+      <c r="K502" s="14" t="n">
+        <v>249.45</v>
+      </c>
+      <c r="M502" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N502" t="inlineStr">
+        <is>
+          <t>25/08/2026 19:06 BRT</t>
+        </is>
+      </c>
+      <c r="O502" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P502" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:38 BRT</t>
+        </is>
+      </c>
+      <c r="Q502" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S502" t="inlineStr">
+        <is>
+          <t>TOCO-II</t>
+        </is>
+      </c>
+      <c r="T502" t="inlineStr">
+        <is>
+          <t>26/08/2026 - QUARTA-FEIRA</t>
+        </is>
+      </c>
+      <c r="U502" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V502" s="9">
+        <f>IFERROR(F502/H502,"")</f>
+        <v/>
+      </c>
+      <c r="W502" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X502" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>BA1</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>RGB(220,20,60)</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>BA-TEIXEIRA_FREITAS</t>
+        </is>
+      </c>
+      <c r="D503" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E503" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="F503" s="13" t="n">
+        <v>1883.8335</v>
+      </c>
+      <c r="G503" s="13" t="n">
+        <v>23949.33</v>
+      </c>
+      <c r="H503" s="13" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>SXL3B60</t>
+        </is>
+      </c>
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ARICLENES SANTOS GARCIA</t>
+        </is>
+      </c>
+      <c r="K503" s="14" t="n">
+        <v>83.84999999999999</v>
+      </c>
+      <c r="M503" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N503" t="inlineStr">
+        <is>
+          <t>25/08/2026 19:06 BRT</t>
+        </is>
+      </c>
+      <c r="O503" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P503" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:38 BRT</t>
+        </is>
+      </c>
+      <c r="Q503" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S503" t="inlineStr">
+        <is>
+          <t>TOCO-III</t>
+        </is>
+      </c>
+      <c r="T503" t="inlineStr">
+        <is>
+          <t>26/08/2026 - QUARTA-FEIRA</t>
+        </is>
+      </c>
+      <c r="U503" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V503" s="9">
+        <f>IFERROR(F503/H503,"")</f>
+        <v/>
+      </c>
+      <c r="W503" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X503" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>BA18</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>RGB(255,140,0)</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>BA-PORTO_CENTRO</t>
+        </is>
+      </c>
+      <c r="D504" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="E504" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="F504" s="13" t="n">
+        <v>2631.2306</v>
+      </c>
+      <c r="G504" s="13" t="n">
+        <v>43006.38</v>
+      </c>
+      <c r="H504" s="13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>TQG6B12</t>
+        </is>
+      </c>
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, DIRCEU KATO KATAYAMA</t>
+        </is>
+      </c>
+      <c r="K504" s="14" t="n">
+        <v>499.86</v>
+      </c>
+      <c r="M504" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N504" t="inlineStr">
+        <is>
+          <t>26/08/2026 06:59 BRT</t>
+        </is>
+      </c>
+      <c r="O504" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P504" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:38 BRT</t>
+        </is>
+      </c>
+      <c r="Q504" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>DIRCEU KATO KATAYAMA</t>
+        </is>
+      </c>
+      <c r="S504" t="inlineStr">
+        <is>
+          <t>TOCO-II</t>
+        </is>
+      </c>
+      <c r="T504" t="inlineStr">
+        <is>
+          <t>26/08/2026 - QUARTA-FEIRA</t>
+        </is>
+      </c>
+      <c r="U504" t="inlineStr">
+        <is>
+          <t>Em Deslocamento</t>
+        </is>
+      </c>
+      <c r="V504" s="9">
+        <f>IFERROR(F504/H504,"")</f>
+        <v/>
+      </c>
+      <c r="W504" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X504" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>SF10</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>RGB(128,0,128)</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>BA-PRADO II</t>
+        </is>
+      </c>
+      <c r="D505" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E505" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F505" s="13" t="n">
+        <v>201.4</v>
+      </c>
+      <c r="G505" s="13" t="n">
+        <v>1272</v>
+      </c>
+      <c r="H505" s="13" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>TPP2C65</t>
+        </is>
+      </c>
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ROBERTO COELHO SANTOS</t>
+        </is>
+      </c>
+      <c r="K505" s="14" t="n">
+        <v>293.66</v>
+      </c>
+      <c r="M505" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N505" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:35 BRT</t>
+        </is>
+      </c>
+      <c r="O505" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P505" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:26 BRT</t>
+        </is>
+      </c>
+      <c r="Q505" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S505" t="inlineStr">
+        <is>
+          <t>TOCO-III</t>
+        </is>
+      </c>
+      <c r="T505" t="inlineStr">
+        <is>
+          <t>26/08/2026 - SUL-FRIOS QUARTA</t>
+        </is>
+      </c>
+      <c r="U505" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V505" s="9">
+        <f>IFERROR(F505/H505,"")</f>
+        <v/>
+      </c>
+      <c r="W505" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X505" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>BPS4</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>RGB(0,0,255)</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>BA-TRANCOSO</t>
+        </is>
+      </c>
+      <c r="D506" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="E506" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F506" s="13" t="n">
+        <v>1314.2162</v>
+      </c>
+      <c r="G506" s="13" t="n">
+        <v>40528.75</v>
+      </c>
+      <c r="H506" s="13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>TQG6D12</t>
+        </is>
+      </c>
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, GIOVANI DA SILVA PRATA</t>
+        </is>
+      </c>
+      <c r="K506" s="14" t="n">
+        <v>379.62</v>
+      </c>
+      <c r="M506" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N506" t="inlineStr">
+        <is>
+          <t>25/08/2026 16:58 BRT</t>
+        </is>
+      </c>
+      <c r="O506" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P506" t="inlineStr">
+        <is>
+          <t>25/08/2026 16:14 BRT</t>
+        </is>
+      </c>
+      <c r="Q506" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S506" t="inlineStr">
+        <is>
+          <t>TOCO-II</t>
+        </is>
+      </c>
+      <c r="T506" t="inlineStr">
+        <is>
+          <t>26/08/2026 - PORTO-IMPORT QUARTA</t>
+        </is>
+      </c>
+      <c r="U506" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V506" s="9">
+        <f>IFERROR(F506/H506,"")</f>
+        <v/>
+      </c>
+      <c r="W506" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X506" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>SF8</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>RGB(70,130,180)</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>BA-ITAMARAJU</t>
+        </is>
+      </c>
+      <c r="D507" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E507" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="F507" s="13" t="n">
+        <v>1668.69</v>
+      </c>
+      <c r="G507" s="13" t="n">
+        <v>24726.2</v>
+      </c>
+      <c r="H507" s="13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>TQG6C72</t>
+        </is>
+      </c>
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ALBERTO SANTOS</t>
+        </is>
+      </c>
+      <c r="K507" s="14" t="n">
+        <v>205.52</v>
+      </c>
+      <c r="M507" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N507" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:54 BRT</t>
+        </is>
+      </c>
+      <c r="O507" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P507" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:09 BRT</t>
+        </is>
+      </c>
+      <c r="Q507" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S507" t="inlineStr">
+        <is>
+          <t>TOCO-II</t>
+        </is>
+      </c>
+      <c r="T507" t="inlineStr">
+        <is>
+          <t>26/08/2026 - SUL-FRIOS QUARTA</t>
+        </is>
+      </c>
+      <c r="U507" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V507" s="9">
+        <f>IFERROR(F507/H507,"")</f>
+        <v/>
+      </c>
+      <c r="W507" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X507" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>SF9</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>RGB(128,0,128)</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>BA-GUARATINGA</t>
+        </is>
+      </c>
+      <c r="D508" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="E508" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="F508" s="13" t="n">
+        <v>2294.8142</v>
+      </c>
+      <c r="G508" s="13" t="n">
+        <v>32652.94</v>
+      </c>
+      <c r="H508" s="13" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>TPP2E45</t>
+        </is>
+      </c>
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, THIAGO MACHADO DE SOUZA</t>
+        </is>
+      </c>
+      <c r="K508" s="14" t="n">
+        <v>166.91</v>
+      </c>
+      <c r="M508" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N508" t="inlineStr">
+        <is>
+          <t>25/08/2026 21:01 BRT</t>
+        </is>
+      </c>
+      <c r="O508" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P508" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:09 BRT</t>
+        </is>
+      </c>
+      <c r="Q508" t="inlineStr">
+        <is>
+          <t>mobilecommunicator@roadnet.com</t>
+        </is>
+      </c>
+      <c r="R508" t="inlineStr">
+        <is>
+          <t xml:space="preserve">THIAGO MACHADO DE SOUZA </t>
+        </is>
+      </c>
+      <c r="S508" t="inlineStr">
+        <is>
+          <t>TOCO-III</t>
+        </is>
+      </c>
+      <c r="T508" t="inlineStr">
+        <is>
+          <t>26/08/2026 - SUL-FRIOS QUARTA</t>
+        </is>
+      </c>
+      <c r="U508" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V508" s="9">
+        <f>IFERROR(F508/H508,"")</f>
+        <v/>
+      </c>
+      <c r="W508" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X508" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>BPS2</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>RGB(0,128,0)</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>BA-ARAIAL_DAJUDA</t>
+        </is>
+      </c>
+      <c r="D509" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="E509" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="F509" s="13" t="n">
+        <v>1710.475</v>
+      </c>
+      <c r="G509" s="13" t="n">
+        <v>24672.47</v>
+      </c>
+      <c r="H509" s="13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>TQG6D22</t>
+        </is>
+      </c>
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, FABIANO JESUS DA HORA</t>
+        </is>
+      </c>
+      <c r="K509" s="14" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="M509" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N509" t="inlineStr">
+        <is>
+          <t>25/08/2026 16:58 BRT</t>
+        </is>
+      </c>
+      <c r="O509" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P509" t="inlineStr">
+        <is>
+          <t>25/08/2026 16:14 BRT</t>
+        </is>
+      </c>
+      <c r="Q509" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S509" t="inlineStr">
+        <is>
+          <t>TOCO-II</t>
+        </is>
+      </c>
+      <c r="T509" t="inlineStr">
+        <is>
+          <t>26/08/2026 - PORTO-IMPORT QUARTA</t>
+        </is>
+      </c>
+      <c r="U509" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V509" s="9">
+        <f>IFERROR(F509/H509,"")</f>
+        <v/>
+      </c>
+      <c r="W509" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X509" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>BPS1</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>RGB(220,20,60)</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>BA-PORTO_CENTRO-ORLA</t>
+        </is>
+      </c>
+      <c r="D510" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="E510" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="F510" s="13" t="n">
+        <v>1322.7313</v>
+      </c>
+      <c r="G510" s="13" t="n">
+        <v>19864.75</v>
+      </c>
+      <c r="H510" s="13" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>PJN2J39</t>
+        </is>
+      </c>
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, AMARILTON JESUS SANTOS</t>
+        </is>
+      </c>
+      <c r="K510" s="14" t="n">
+        <v>56.47</v>
+      </c>
+      <c r="M510" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N510" t="inlineStr">
+        <is>
+          <t>25/08/2026 16:58 BRT</t>
+        </is>
+      </c>
+      <c r="O510" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P510" t="inlineStr">
+        <is>
+          <t>25/08/2026 16:14 BRT</t>
+        </is>
+      </c>
+      <c r="Q510" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S510" t="inlineStr">
+        <is>
+          <t>TOCO</t>
+        </is>
+      </c>
+      <c r="T510" t="inlineStr">
+        <is>
+          <t>26/08/2026 - PORTO-IMPORT QUARTA</t>
+        </is>
+      </c>
+      <c r="U510" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V510" s="9">
+        <f>IFERROR(F510/H510,"")</f>
+        <v/>
+      </c>
+      <c r="W510" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X510" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>SF5</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>RGB(255,105,180)</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>BA-ITABELA</t>
+        </is>
+      </c>
+      <c r="D511" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="E511" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="F511" s="13" t="n">
+        <v>4792.0458</v>
+      </c>
+      <c r="G511" s="13" t="n">
+        <v>67841.53</v>
+      </c>
+      <c r="H511" s="13" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>PKU5I64</t>
+        </is>
+      </c>
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ZENILTON FERNANDES DA SILVA</t>
+        </is>
+      </c>
+      <c r="K511" s="14" t="n">
+        <v>82.56</v>
+      </c>
+      <c r="M511" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N511" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:35 BRT</t>
+        </is>
+      </c>
+      <c r="O511" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P511" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:09 BRT</t>
+        </is>
+      </c>
+      <c r="Q511" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S511" t="inlineStr">
+        <is>
+          <t>TOCO-III</t>
+        </is>
+      </c>
+      <c r="T511" t="inlineStr">
+        <is>
+          <t>26/08/2026 - SUL-FRIOS QUARTA</t>
+        </is>
+      </c>
+      <c r="U511" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V511" s="9">
+        <f>IFERROR(F511/H511,"")</f>
+        <v/>
+      </c>
+      <c r="W511" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X511" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>SF7</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>RGB(205,92,92)</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>BA-PRADO</t>
+        </is>
+      </c>
+      <c r="D512" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="E512" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="F512" s="13" t="n">
+        <v>3743.571</v>
+      </c>
+      <c r="G512" s="13" t="n">
+        <v>51556.71</v>
+      </c>
+      <c r="H512" s="13" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>TPP2C65</t>
+        </is>
+      </c>
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, ROBERTO COELHO SANTOS</t>
+        </is>
+      </c>
+      <c r="K512" s="14" t="n">
+        <v>363.36</v>
+      </c>
+      <c r="M512" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N512" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:35 BRT</t>
+        </is>
+      </c>
+      <c r="O512" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P512" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:09 BRT</t>
+        </is>
+      </c>
+      <c r="Q512" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S512" t="inlineStr">
+        <is>
+          <t>TOCO-III</t>
+        </is>
+      </c>
+      <c r="T512" t="inlineStr">
+        <is>
+          <t>26/08/2026 - SUL-FRIOS QUARTA</t>
+        </is>
+      </c>
+      <c r="U512" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V512" s="9">
+        <f>IFERROR(F512/H512,"")</f>
+        <v/>
+      </c>
+      <c r="W512" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X512" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>SF1</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>RGB(220,20,60)</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>BA-GANDU</t>
+        </is>
+      </c>
+      <c r="D513" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="E513" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F513" s="13" t="n">
+        <v>2667.1273</v>
+      </c>
+      <c r="G513" s="13" t="n">
+        <v>45482.03</v>
+      </c>
+      <c r="H513" s="13" t="n">
+        <v>6500</v>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>TQG7B12</t>
+        </is>
+      </c>
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, AGUINALDO DA SILVA SANTOS</t>
+        </is>
+      </c>
+      <c r="K513" s="14" t="n">
+        <v>842.5</v>
+      </c>
+      <c r="M513" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N513" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:35 BRT</t>
+        </is>
+      </c>
+      <c r="O513" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P513" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:09 BRT</t>
+        </is>
+      </c>
+      <c r="Q513" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S513" t="inlineStr">
+        <is>
+          <t>TOCO-II</t>
+        </is>
+      </c>
+      <c r="T513" t="inlineStr">
+        <is>
+          <t>26/08/2026 - SUL-FRIOS QUARTA</t>
+        </is>
+      </c>
+      <c r="U513" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V513" s="9">
+        <f>IFERROR(F513/H513,"")</f>
+        <v/>
+      </c>
+      <c r="W513" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X513" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>SF4</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>RGB(0,0,255)</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>BA-ITACARÉ</t>
+        </is>
+      </c>
+      <c r="D514" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="E514" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="F514" s="13" t="n">
+        <v>5683.29</v>
+      </c>
+      <c r="G514" s="13" t="n">
+        <v>80353.31</v>
+      </c>
+      <c r="H514" s="13" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>TPP3G65</t>
+        </is>
+      </c>
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, JILVAN DE JESUS OLIVEIRA</t>
+        </is>
+      </c>
+      <c r="K514" s="14" t="n">
+        <v>749.8099999999999</v>
+      </c>
+      <c r="M514" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N514" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:54 BRT</t>
+        </is>
+      </c>
+      <c r="O514" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P514" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:09 BRT</t>
+        </is>
+      </c>
+      <c r="Q514" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S514" t="inlineStr">
+        <is>
+          <t>TOCO-III</t>
+        </is>
+      </c>
+      <c r="T514" t="inlineStr">
+        <is>
+          <t>26/08/2026 - SUL-FRIOS QUARTA</t>
+        </is>
+      </c>
+      <c r="U514" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V514" s="9">
+        <f>IFERROR(F514/H514,"")</f>
+        <v/>
+      </c>
+      <c r="W514" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X514" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>SF6</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>RGB(160,82,45)</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>BA-JEQUIE</t>
+        </is>
+      </c>
+      <c r="D515" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="E515" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="F515" s="13" t="n">
+        <v>7094.6602</v>
+      </c>
+      <c r="G515" s="13" t="n">
+        <v>87521.78999999999</v>
+      </c>
+      <c r="H515" s="13" t="n">
+        <v>14000</v>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>ISX3290</t>
+        </is>
+      </c>
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>&lt;&gt;, FABRICIO SANTOS SOUZA</t>
+        </is>
+      </c>
+      <c r="K515" s="14" t="n">
+        <v>893.53</v>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>ANALISTA ROTEIRIZAÇÃO, ROBERTO ALEVES</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>25/08/2026 18:35 BRT</t>
+        </is>
+      </c>
+      <c r="O515" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="P515" t="inlineStr">
+        <is>
+          <t>25/08/2026 17:09 BRT</t>
+        </is>
+      </c>
+      <c r="Q515" t="inlineStr">
+        <is>
+          <t>roberto.silva@dellys.com.br</t>
+        </is>
+      </c>
+      <c r="S515" t="inlineStr">
+        <is>
+          <t>TRUCK-I</t>
+        </is>
+      </c>
+      <c r="T515" t="inlineStr">
+        <is>
+          <t>26/08/2026 - SUL-FRIOS QUARTA</t>
+        </is>
+      </c>
+      <c r="U515" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="V515" s="9">
+        <f>IFERROR(F515/H515,"")</f>
+        <v/>
+      </c>
+      <c r="W515" t="inlineStr">
+        <is>
+          <t>26/08</t>
+        </is>
+      </c>
+      <c r="X515" t="inlineStr">
+        <is>
+          <t>AGO/S5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
